--- a/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34E6A95-F989-49C4-89A3-D12CADBC5A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,7 +37,7 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-BRC-PPO</t>
+    <t>JPS-GL-BRC-PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -49,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +119,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +171,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -400,11 +416,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,7 +434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -426,13 +442,13 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004638</v>
+        <v>4.3960000000000011E-4</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -440,13 +456,13 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0004754000000000001</v>
+        <v>3.5639999999999999E-4</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -454,13 +470,13 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>0.0033869</v>
+        <v>3.3719000000000002E-3</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -468,13 +484,13 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>0.0013899</v>
+        <v>9.5029999999999995E-4</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -482,13 +498,13 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>0.0240776</v>
+        <v>2.38073E-2</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -496,13 +512,13 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>0.0045273</v>
+        <v>2.9309000000000002E-3</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -510,13 +526,13 @@
         <v>128</v>
       </c>
       <c r="C8">
-        <v>0.1518754</v>
+        <v>0.15643599999999999</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -524,13 +540,13 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>0.0179984</v>
+        <v>1.07648E-2</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -538,13 +554,13 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>0.0004756999999999999</v>
+        <v>4.8799999999999999E-4</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -552,13 +568,13 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.0004256</v>
+        <v>3.8509999999999998E-4</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -566,13 +582,13 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>0.0028988</v>
+        <v>2.934E-3</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -580,13 +596,13 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>0.0014189</v>
+        <v>1.0217E-3</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -594,13 +610,13 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>0.0186209</v>
+        <v>1.9111099999999999E-2</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -608,13 +624,13 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>0.0037633</v>
+        <v>2.7238000000000002E-3</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -622,13 +638,13 @@
         <v>128</v>
       </c>
       <c r="C16">
-        <v>0.1221172</v>
+        <v>0.12644179999999999</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -636,13 +652,13 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.0128954</v>
+        <v>1.1424200000000001E-2</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -650,13 +666,13 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>0.0003802</v>
+        <v>3.6840000000000001E-4</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -664,13 +680,13 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>0.0003581</v>
+        <v>3.8289999999999998E-4</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -678,13 +694,13 @@
         <v>32</v>
       </c>
       <c r="C20">
-        <v>0.0024911</v>
+        <v>2.4880000000000002E-3</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -692,13 +708,13 @@
         <v>32</v>
       </c>
       <c r="C21">
-        <v>0.0011095</v>
+        <v>8.5880000000000006E-4</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -706,13 +722,13 @@
         <v>64</v>
       </c>
       <c r="C22">
-        <v>0.0158681</v>
+        <v>1.6137499999999999E-2</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -720,13 +736,13 @@
         <v>64</v>
       </c>
       <c r="C23">
-        <v>0.0030103</v>
+        <v>2.7320999999999999E-3</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -734,13 +750,13 @@
         <v>128</v>
       </c>
       <c r="C24">
-        <v>0.1031649</v>
+        <v>0.1062307</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -748,13 +764,13 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>0.010972</v>
+        <v>1.0248699999999999E-2</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -762,13 +778,13 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>0.0005350999999999999</v>
+        <v>5.4600000000000004E-4</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -776,13 +792,13 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>0.0004423</v>
+        <v>3.4269999999999987E-4</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -790,13 +806,13 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>0.0036208</v>
+        <v>3.6840000000000011E-3</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -804,13 +820,13 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>0.0010345</v>
+        <v>7.7210000000000006E-4</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -818,13 +834,13 @@
         <v>64</v>
       </c>
       <c r="C30">
-        <v>0.0287961</v>
+        <v>3.0356999999999999E-2</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -832,13 +848,13 @@
         <v>64</v>
       </c>
       <c r="C31">
-        <v>0.0030974</v>
+        <v>2.2250999999999998E-3</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -846,13 +862,13 @@
         <v>128</v>
       </c>
       <c r="C32">
-        <v>0.2103159</v>
+        <v>0.21800220000000001</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -860,13 +876,13 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>0.0111757</v>
+        <v>7.606700000000001E-3</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -874,13 +890,13 @@
         <v>16</v>
       </c>
       <c r="C34">
-        <v>0.0007653</v>
+        <v>7.1560000000000005E-4</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -888,13 +904,13 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>0.0004543</v>
+        <v>3.7750000000000001E-4</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -902,13 +918,13 @@
         <v>32</v>
       </c>
       <c r="C36">
-        <v>0.0055339</v>
+        <v>5.5637999999999998E-3</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -916,13 +932,13 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>0.0020277</v>
+        <v>1.1276999999999999E-3</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -930,13 +946,13 @@
         <v>64</v>
       </c>
       <c r="C38">
-        <v>0.0473926</v>
+        <v>4.7600499999999997E-2</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -944,13 +960,13 @@
         <v>64</v>
       </c>
       <c r="C39">
-        <v>0.0066388</v>
+        <v>3.7401000000000001E-3</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -958,13 +974,13 @@
         <v>128</v>
       </c>
       <c r="C40">
-        <v>0.3204569999999999</v>
+        <v>0.32752520000000002</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -972,7 +988,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>0.0244447</v>
+        <v>1.38309E-2</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34E6A95-F989-49C4-89A3-D12CADBC5A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="13">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -37,7 +31,16 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-GL-BRC-PPO</t>
+    <t>BRC</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>JPS</t>
+  </si>
+  <si>
+    <t>PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -55,8 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,21 +122,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -171,7 +166,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -205,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -240,10 +234,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -416,11 +409,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -442,13 +435,13 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>4.3960000000000011E-4</v>
+        <v>0.0004530000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -456,542 +449,1382 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>3.5639999999999999E-4</v>
+        <v>0.0003911</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>3.3719000000000002E-3</v>
+        <v>0.0003456</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>9.5029999999999995E-4</v>
+        <v>0.0003186</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>2.38073E-2</v>
+        <v>0.0005079</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>2.9309000000000002E-3</v>
+        <v>0.0032506</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>0.15643599999999999</v>
+        <v>0.0012508</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>1.07648E-2</v>
+        <v>0.0017691</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C10">
-        <v>4.8799999999999999E-4</v>
+        <v>0.0010452</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C11">
-        <v>3.8509999999999998E-4</v>
+        <v>0.0034012</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>2.934E-3</v>
+        <v>0.0238787</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>5</v>
       </c>
       <c r="B13">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>1.0217E-3</v>
+        <v>0.005478100000000001</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>64</v>
       </c>
       <c r="C14">
-        <v>1.9111099999999999E-2</v>
+        <v>0.0118224</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>64</v>
       </c>
       <c r="C15">
-        <v>2.7238000000000002E-3</v>
+        <v>0.0034616</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C16">
-        <v>0.12644179999999999</v>
+        <v>0.0230443</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17">
         <v>128</v>
       </c>
       <c r="C17">
-        <v>1.1424200000000001E-2</v>
+        <v>0.1490245</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C18">
-        <v>3.6840000000000001E-4</v>
+        <v>0.0402807</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C19">
-        <v>3.8289999999999998E-4</v>
+        <v>0.08020040000000001</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C20">
-        <v>2.4880000000000002E-3</v>
+        <v>0.0140568</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C21">
-        <v>8.5880000000000006E-4</v>
+        <v>0.1485451</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>1.6137499999999999E-2</v>
+        <v>0.0004585</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>2.7320999999999999E-3</v>
+        <v>0.0005399</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>0.1062307</v>
+        <v>0.0003932</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25">
-        <v>128</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>1.0248699999999999E-2</v>
+        <v>0.0003333</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>16</v>
       </c>
       <c r="C26">
-        <v>5.4600000000000004E-4</v>
+        <v>0.000512</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>3.4269999999999987E-4</v>
+        <v>0.0028168</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>32</v>
       </c>
       <c r="C28">
-        <v>3.6840000000000011E-3</v>
+        <v>0.0018485</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>32</v>
       </c>
       <c r="C29">
-        <v>7.7210000000000006E-4</v>
+        <v>0.0023093</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B30">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C30">
-        <v>3.0356999999999999E-2</v>
+        <v>0.0009808</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>2.2250999999999998E-3</v>
+        <v>0.0029314</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>4</v>
       </c>
       <c r="B32">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C32">
-        <v>0.21800220000000001</v>
+        <v>0.0190411</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>5</v>
       </c>
       <c r="B33">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="C33">
-        <v>7.606700000000001E-3</v>
+        <v>0.0163242</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C34">
-        <v>7.1560000000000005E-4</v>
+        <v>0.0154216</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C35">
-        <v>3.7750000000000001E-4</v>
+        <v>0.003392399999999999</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C36">
-        <v>5.5637999999999998E-3</v>
+        <v>0.0183713</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C37">
-        <v>1.1276999999999999E-3</v>
+        <v>0.121997</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B38">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C38">
-        <v>4.7600499999999997E-2</v>
+        <v>0.1526633</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B39">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="C39">
-        <v>3.7401000000000001E-3</v>
+        <v>0.1059115</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B40">
         <v>128</v>
       </c>
       <c r="C40">
-        <v>0.32752520000000002</v>
+        <v>0.0122929</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B41">
         <v>128</v>
       </c>
       <c r="C41">
-        <v>1.38309E-2</v>
+        <v>0.1215531</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>0.0003786</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>0.0002895</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>0.0003137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>0.0003942</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46">
+        <v>16</v>
+      </c>
+      <c r="C46">
+        <v>0.0004014</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>32</v>
+      </c>
+      <c r="C47">
+        <v>0.002459499999999999</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48">
+        <v>32</v>
+      </c>
+      <c r="C48">
+        <v>0.0013014</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>0.0018837</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50">
+        <v>32</v>
+      </c>
+      <c r="C50">
+        <v>0.0012408</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51">
+        <v>32</v>
+      </c>
+      <c r="C51">
+        <v>0.0025718</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>64</v>
+      </c>
+      <c r="C52">
+        <v>0.015765</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>0.008706700000000001</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>64</v>
+      </c>
+      <c r="C54">
+        <v>0.0125769</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>64</v>
+      </c>
+      <c r="C55">
+        <v>0.0046645</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>64</v>
+      </c>
+      <c r="C56">
+        <v>0.0172327</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>128</v>
+      </c>
+      <c r="C57">
+        <v>0.1020895</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58">
+        <v>128</v>
+      </c>
+      <c r="C58">
+        <v>0.0652737</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>128</v>
+      </c>
+      <c r="C59">
+        <v>0.08295180000000001</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60">
+        <v>128</v>
+      </c>
+      <c r="C60">
+        <v>0.0199562</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61">
+        <v>128</v>
+      </c>
+      <c r="C61">
+        <v>0.102782</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>0.0005406</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>0.000384</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64">
+        <v>16</v>
+      </c>
+      <c r="C64">
+        <v>0.0004287</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>0.0004063000000000001</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>16</v>
+      </c>
+      <c r="C66">
+        <v>0.0005910999999999999</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67">
+        <v>32</v>
+      </c>
+      <c r="C67">
+        <v>0.0035912</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>32</v>
+      </c>
+      <c r="C68">
+        <v>0.0013739</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69">
+        <v>32</v>
+      </c>
+      <c r="C69">
+        <v>0.0025759</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70">
+        <v>32</v>
+      </c>
+      <c r="C70">
+        <v>0.0012948</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71">
+        <v>32</v>
+      </c>
+      <c r="C71">
+        <v>0.0036794</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72">
+        <v>64</v>
+      </c>
+      <c r="C72">
+        <v>0.0287193</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>64</v>
+      </c>
+      <c r="C73">
+        <v>0.0054597</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74">
+        <v>64</v>
+      </c>
+      <c r="C74">
+        <v>0.01683</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>0.004711600000000001</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76">
+        <v>64</v>
+      </c>
+      <c r="C76">
+        <v>0.027812</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77">
+        <v>128</v>
+      </c>
+      <c r="C77">
+        <v>0.208237</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78">
+        <v>128</v>
+      </c>
+      <c r="C78">
+        <v>0.0346657</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>128</v>
+      </c>
+      <c r="C79">
+        <v>0.1163257</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80">
+        <v>128</v>
+      </c>
+      <c r="C80">
+        <v>0.01906</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81">
+        <v>128</v>
+      </c>
+      <c r="C81">
+        <v>0.2072281999999999</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82">
+        <v>16</v>
+      </c>
+      <c r="C82">
+        <v>0.000717</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83">
+        <v>16</v>
+      </c>
+      <c r="C83">
+        <v>0.0004643000000000001</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>0.0006058</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>0.0005839</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86">
+        <v>16</v>
+      </c>
+      <c r="C86">
+        <v>0.0008386999999999998</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87">
+        <v>32</v>
+      </c>
+      <c r="C87">
+        <v>0.0055118</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88">
+        <v>32</v>
+      </c>
+      <c r="C88">
+        <v>0.001511</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>32</v>
+      </c>
+      <c r="C89">
+        <v>0.0034278</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90">
+        <v>32</v>
+      </c>
+      <c r="C90">
+        <v>0.0020146</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91">
+        <v>32</v>
+      </c>
+      <c r="C91">
+        <v>0.0055471</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92">
+        <v>64</v>
+      </c>
+      <c r="C92">
+        <v>0.0465013</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93">
+        <v>64</v>
+      </c>
+      <c r="C93">
+        <v>0.0108756</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>6</v>
+      </c>
+      <c r="B94">
+        <v>64</v>
+      </c>
+      <c r="C94">
+        <v>0.0223417</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95">
+        <v>64</v>
+      </c>
+      <c r="C95">
+        <v>0.007431200000000001</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96">
+        <v>64</v>
+      </c>
+      <c r="C96">
+        <v>0.04703710000000001</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>4</v>
+      </c>
+      <c r="B97">
+        <v>128</v>
+      </c>
+      <c r="C97">
+        <v>0.3183174</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98">
+        <v>128</v>
+      </c>
+      <c r="C98">
+        <v>0.092317</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99">
+        <v>128</v>
+      </c>
+      <c r="C99">
+        <v>0.1514367</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100">
+        <v>128</v>
+      </c>
+      <c r="C100">
+        <v>0.030449</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101">
+        <v>128</v>
+      </c>
+      <c r="C101">
+        <v>0.3183032</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -435,7 +435,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004530000000000001</v>
+        <v>0.0004822</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -449,7 +449,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0003911</v>
+        <v>0.0004101</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -463,7 +463,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>0.0003456</v>
+        <v>0.0003179</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -477,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>0.0003186</v>
+        <v>0.0003319</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0005079</v>
+        <v>0.0005113</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -505,7 +505,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>0.0032506</v>
+        <v>0.0034743</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -519,7 +519,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>0.0012508</v>
+        <v>0.0013158</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -533,7 +533,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>0.0017691</v>
+        <v>0.0018366</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -547,7 +547,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>0.0010452</v>
+        <v>0.0010794</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0034012</v>
+        <v>0.0035126</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -575,7 +575,7 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>0.0238787</v>
+        <v>0.025808</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>0.005478100000000001</v>
+        <v>0.005923699999999999</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -603,7 +603,7 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>0.0118224</v>
+        <v>0.0129962</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -617,7 +617,7 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>0.0034616</v>
+        <v>0.0036981</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -631,7 +631,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.0230443</v>
+        <v>0.0248513</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -645,7 +645,7 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.1490245</v>
+        <v>0.15967</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>0.0402807</v>
+        <v>0.0429991</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -673,7 +673,7 @@
         <v>128</v>
       </c>
       <c r="C19">
-        <v>0.08020040000000001</v>
+        <v>0.08562030000000001</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>128</v>
       </c>
       <c r="C20">
-        <v>0.0140568</v>
+        <v>0.0150779</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -701,7 +701,7 @@
         <v>128</v>
       </c>
       <c r="C21">
-        <v>0.1485451</v>
+        <v>0.1598635</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -715,7 +715,7 @@
         <v>16</v>
       </c>
       <c r="C22">
-        <v>0.0004585</v>
+        <v>0.0005046</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
@@ -729,7 +729,7 @@
         <v>16</v>
       </c>
       <c r="C23">
-        <v>0.0005399</v>
+        <v>0.00055</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -743,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C24">
-        <v>0.0003932</v>
+        <v>0.0004154</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -757,7 +757,7 @@
         <v>16</v>
       </c>
       <c r="C25">
-        <v>0.0003333</v>
+        <v>0.0003521</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -771,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>0.000512</v>
+        <v>0.0006652</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -785,7 +785,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0028168</v>
+        <v>0.0029849</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>0.0018485</v>
+        <v>0.0019769</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -813,7 +813,7 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>0.0023093</v>
+        <v>0.002414</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
@@ -827,7 +827,7 @@
         <v>32</v>
       </c>
       <c r="C30">
-        <v>0.0009808</v>
+        <v>0.0010381</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -841,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <v>0.0029314</v>
+        <v>0.0030295</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -855,7 +855,7 @@
         <v>64</v>
       </c>
       <c r="C32">
-        <v>0.0190411</v>
+        <v>0.0196066</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>0.0163242</v>
+        <v>0.0173749</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>64</v>
       </c>
       <c r="C34">
-        <v>0.0154216</v>
+        <v>0.0163651</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -897,7 +897,7 @@
         <v>64</v>
       </c>
       <c r="C35">
-        <v>0.003392399999999999</v>
+        <v>0.0034979</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -911,7 +911,7 @@
         <v>64</v>
       </c>
       <c r="C36">
-        <v>0.0183713</v>
+        <v>0.0197748</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -925,7 +925,7 @@
         <v>128</v>
       </c>
       <c r="C37">
-        <v>0.121997</v>
+        <v>0.1302875</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>0.1526633</v>
+        <v>0.1626759</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -953,7 +953,7 @@
         <v>128</v>
       </c>
       <c r="C39">
-        <v>0.1059115</v>
+        <v>0.1147033</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -967,7 +967,7 @@
         <v>128</v>
       </c>
       <c r="C40">
-        <v>0.0122929</v>
+        <v>0.0127862</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -981,7 +981,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>0.1215531</v>
+        <v>0.1311289</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
@@ -995,7 +995,7 @@
         <v>16</v>
       </c>
       <c r="C42">
-        <v>0.0003786</v>
+        <v>0.000411</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>0.0002895</v>
+        <v>0.0003135</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
       <c r="C44">
-        <v>0.0003137</v>
+        <v>0.0003295</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1037,7 +1037,7 @@
         <v>16</v>
       </c>
       <c r="C45">
-        <v>0.0003942</v>
+        <v>0.0004089</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>0.0004014</v>
+        <v>0.0004338</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1065,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="C47">
-        <v>0.002459499999999999</v>
+        <v>0.0025615</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="C48">
-        <v>0.0013014</v>
+        <v>0.0014422</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>32</v>
       </c>
       <c r="C49">
-        <v>0.0018837</v>
+        <v>0.0020269</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>32</v>
       </c>
       <c r="C50">
-        <v>0.0012408</v>
+        <v>0.0013142</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -1121,7 +1121,7 @@
         <v>32</v>
       </c>
       <c r="C51">
-        <v>0.0025718</v>
+        <v>0.002598899999999999</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -1135,7 +1135,7 @@
         <v>64</v>
       </c>
       <c r="C52">
-        <v>0.015765</v>
+        <v>0.0168613</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>0.008706700000000001</v>
+        <v>0.0093718</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>64</v>
       </c>
       <c r="C54">
-        <v>0.0125769</v>
+        <v>0.0135943</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -1177,7 +1177,7 @@
         <v>64</v>
       </c>
       <c r="C55">
-        <v>0.0046645</v>
+        <v>0.004973300000000001</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>0.0172327</v>
+        <v>0.0171851</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -1205,7 +1205,7 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>0.1020895</v>
+        <v>0.1104541</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>0.0652737</v>
+        <v>0.07056939999999999</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>128</v>
       </c>
       <c r="C59">
-        <v>0.08295180000000001</v>
+        <v>0.08971359999999999</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -1247,7 +1247,7 @@
         <v>128</v>
       </c>
       <c r="C60">
-        <v>0.0199562</v>
+        <v>0.0216076</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -1261,7 +1261,7 @@
         <v>128</v>
       </c>
       <c r="C61">
-        <v>0.102782</v>
+        <v>0.1110167</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>16</v>
       </c>
       <c r="C62">
-        <v>0.0005406</v>
+        <v>0.0006736</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -1289,7 +1289,7 @@
         <v>16</v>
       </c>
       <c r="C63">
-        <v>0.000384</v>
+        <v>0.0003932000000000001</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C64">
-        <v>0.0004287</v>
+        <v>0.000454</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -1317,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C65">
-        <v>0.0004063000000000001</v>
+        <v>0.0004305</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="C66">
-        <v>0.0005910999999999999</v>
+        <v>0.0007059999999999999</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -1345,7 +1345,7 @@
         <v>32</v>
       </c>
       <c r="C67">
-        <v>0.0035912</v>
+        <v>0.003875100000000001</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>0.0013739</v>
+        <v>0.0014195</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -1373,7 +1373,7 @@
         <v>32</v>
       </c>
       <c r="C69">
-        <v>0.0025759</v>
+        <v>0.002692</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -1387,7 +1387,7 @@
         <v>32</v>
       </c>
       <c r="C70">
-        <v>0.0012948</v>
+        <v>0.0013392</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -1401,7 +1401,7 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>0.0036794</v>
+        <v>0.0039451</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -1415,7 +1415,7 @@
         <v>64</v>
       </c>
       <c r="C72">
-        <v>0.0287193</v>
+        <v>0.0296328</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>0.0054597</v>
+        <v>0.0058033</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1443,7 +1443,7 @@
         <v>64</v>
       </c>
       <c r="C74">
-        <v>0.01683</v>
+        <v>0.0183267</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -1457,7 +1457,7 @@
         <v>64</v>
       </c>
       <c r="C75">
-        <v>0.004711600000000001</v>
+        <v>0.0050223</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -1471,7 +1471,7 @@
         <v>64</v>
       </c>
       <c r="C76">
-        <v>0.027812</v>
+        <v>0.029346</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -1485,7 +1485,7 @@
         <v>128</v>
       </c>
       <c r="C77">
-        <v>0.208237</v>
+        <v>0.2242598</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>0.0346657</v>
+        <v>0.0368362</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1513,7 +1513,7 @@
         <v>128</v>
       </c>
       <c r="C79">
-        <v>0.1163257</v>
+        <v>0.1254835</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -1527,7 +1527,7 @@
         <v>128</v>
       </c>
       <c r="C80">
-        <v>0.01906</v>
+        <v>0.0206832</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>128</v>
       </c>
       <c r="C81">
-        <v>0.2072281999999999</v>
+        <v>0.2232106</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -1555,7 +1555,7 @@
         <v>16</v>
       </c>
       <c r="C82">
-        <v>0.000717</v>
+        <v>0.0007793</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
@@ -1569,7 +1569,7 @@
         <v>16</v>
       </c>
       <c r="C83">
-        <v>0.0004643000000000001</v>
+        <v>0.0004352</v>
       </c>
       <c r="D83" t="s">
         <v>12</v>
@@ -1583,7 +1583,7 @@
         <v>16</v>
       </c>
       <c r="C84">
-        <v>0.0006058</v>
+        <v>0.0006098</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
@@ -1597,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="C85">
-        <v>0.0005839</v>
+        <v>0.0006093</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
@@ -1611,7 +1611,7 @@
         <v>16</v>
       </c>
       <c r="C86">
-        <v>0.0008386999999999998</v>
+        <v>0.0008636999999999999</v>
       </c>
       <c r="D86" t="s">
         <v>12</v>
@@ -1625,7 +1625,7 @@
         <v>32</v>
       </c>
       <c r="C87">
-        <v>0.0055118</v>
+        <v>0.0057743</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
@@ -1639,7 +1639,7 @@
         <v>32</v>
       </c>
       <c r="C88">
-        <v>0.001511</v>
+        <v>0.0015813</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -1653,7 +1653,7 @@
         <v>32</v>
       </c>
       <c r="C89">
-        <v>0.0034278</v>
+        <v>0.0035952</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
@@ -1667,7 +1667,7 @@
         <v>32</v>
       </c>
       <c r="C90">
-        <v>0.0020146</v>
+        <v>0.0021138</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
@@ -1681,7 +1681,7 @@
         <v>32</v>
       </c>
       <c r="C91">
-        <v>0.0055471</v>
+        <v>0.0058417</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
@@ -1695,7 +1695,7 @@
         <v>64</v>
       </c>
       <c r="C92">
-        <v>0.0465013</v>
+        <v>0.0501117</v>
       </c>
       <c r="D92" t="s">
         <v>12</v>
@@ -1709,7 +1709,7 @@
         <v>64</v>
       </c>
       <c r="C93">
-        <v>0.0108756</v>
+        <v>0.0118541</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -1723,7 +1723,7 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>0.0223417</v>
+        <v>0.023993</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -1737,7 +1737,7 @@
         <v>64</v>
       </c>
       <c r="C95">
-        <v>0.007431200000000001</v>
+        <v>0.0080479</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -1751,7 +1751,7 @@
         <v>64</v>
       </c>
       <c r="C96">
-        <v>0.04703710000000001</v>
+        <v>0.0502154</v>
       </c>
       <c r="D96" t="s">
         <v>12</v>
@@ -1765,7 +1765,7 @@
         <v>128</v>
       </c>
       <c r="C97">
-        <v>0.3183174</v>
+        <v>0.340181</v>
       </c>
       <c r="D97" t="s">
         <v>12</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>0.092317</v>
+        <v>0.09822610000000001</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
@@ -1793,7 +1793,7 @@
         <v>128</v>
       </c>
       <c r="C99">
-        <v>0.1514367</v>
+        <v>0.1622748</v>
       </c>
       <c r="D99" t="s">
         <v>12</v>
@@ -1807,7 +1807,7 @@
         <v>128</v>
       </c>
       <c r="C100">
-        <v>0.030449</v>
+        <v>0.03305300000000001</v>
       </c>
       <c r="D100" t="s">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>128</v>
       </c>
       <c r="C101">
-        <v>0.3183032</v>
+        <v>0.3422766</v>
       </c>
       <c r="D101" t="s">
         <v>12</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Waktu Pencarian.xlsx
@@ -435,7 +435,7 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004822</v>
+        <v>0.0005032000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -449,7 +449,7 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>0.0004101</v>
+        <v>0.0001963</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -463,7 +463,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>0.0003179</v>
+        <v>0.0003287</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -477,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>0.0003319</v>
+        <v>0.0003375</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0005113</v>
+        <v>0.0004804</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -505,7 +505,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>0.0034743</v>
+        <v>0.003523399999999999</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -519,7 +519,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>0.0013158</v>
+        <v>0.0006369999999999999</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -533,7 +533,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>0.0018366</v>
+        <v>0.0018679</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -547,7 +547,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>0.0010794</v>
+        <v>0.0011568</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0035126</v>
+        <v>0.0034676</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -575,7 +575,7 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>0.025808</v>
+        <v>0.0245314</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>0.005923699999999999</v>
+        <v>0.0020404</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -603,7 +603,7 @@
         <v>64</v>
       </c>
       <c r="C14">
-        <v>0.0129962</v>
+        <v>0.0127819</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -617,7 +617,7 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>0.0036981</v>
+        <v>0.0036926</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -631,7 +631,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.0248513</v>
+        <v>0.0243821</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -645,7 +645,7 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.15967</v>
+        <v>0.1620138</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>0.0429991</v>
+        <v>0.0074792</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -673,7 +673,7 @@
         <v>128</v>
       </c>
       <c r="C19">
-        <v>0.08562030000000001</v>
+        <v>0.08665039999999999</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -687,7 +687,7 @@
         <v>128</v>
       </c>
       <c r="C20">
-        <v>0.0150779</v>
+        <v>0.015071</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -701,7 +701,7 @@
         <v>128</v>
       </c>
       <c r="C21">
-        <v>0.1598635</v>
+        <v>0.1615691</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -715,7 +715,7 @@
         <v>16</v>
       </c>
       <c r="C22">
-        <v>0.0005046</v>
+        <v>0.0004917</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
@@ -729,7 +729,7 @@
         <v>16</v>
       </c>
       <c r="C23">
-        <v>0.00055</v>
+        <v>0.0002705</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -743,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="C24">
-        <v>0.0004154</v>
+        <v>0.0004196</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -757,7 +757,7 @@
         <v>16</v>
       </c>
       <c r="C25">
-        <v>0.0003521</v>
+        <v>0.0004123</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -771,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>0.0006652</v>
+        <v>0.0004839999999999999</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -785,7 +785,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0029849</v>
+        <v>0.0029884</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>0.0019769</v>
+        <v>0.0009784999999999998</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -813,7 +813,7 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>0.002414</v>
+        <v>0.002399</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
@@ -827,7 +827,7 @@
         <v>32</v>
       </c>
       <c r="C30">
-        <v>0.0010381</v>
+        <v>0.0010203</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -841,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <v>0.0030295</v>
+        <v>0.0029943</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -855,7 +855,7 @@
         <v>64</v>
       </c>
       <c r="C32">
-        <v>0.0196066</v>
+        <v>0.0202147</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>0.0173749</v>
+        <v>0.005393600000000001</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>64</v>
       </c>
       <c r="C34">
-        <v>0.0163651</v>
+        <v>0.0166019</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -897,7 +897,7 @@
         <v>64</v>
       </c>
       <c r="C35">
-        <v>0.0034979</v>
+        <v>0.0035396</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -911,7 +911,7 @@
         <v>64</v>
       </c>
       <c r="C36">
-        <v>0.0197748</v>
+        <v>0.0199947</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -925,7 +925,7 @@
         <v>128</v>
       </c>
       <c r="C37">
-        <v>0.1302875</v>
+        <v>0.1326106</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>0.1626759</v>
+        <v>0.0299984</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -953,7 +953,7 @@
         <v>128</v>
       </c>
       <c r="C39">
-        <v>0.1147033</v>
+        <v>0.1168257</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -967,7 +967,7 @@
         <v>128</v>
       </c>
       <c r="C40">
-        <v>0.0127862</v>
+        <v>0.0133145</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -981,7 +981,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>0.1311289</v>
+        <v>0.1322051</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
@@ -995,7 +995,7 @@
         <v>16</v>
       </c>
       <c r="C42">
-        <v>0.000411</v>
+        <v>0.0003857</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>0.0003135</v>
+        <v>0.0001989</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
       <c r="C44">
-        <v>0.0003295</v>
+        <v>0.0003264</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1037,7 +1037,7 @@
         <v>16</v>
       </c>
       <c r="C45">
-        <v>0.0004089</v>
+        <v>0.0004107000000000001</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>0.0004338</v>
+        <v>0.0003958</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1065,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="C47">
-        <v>0.0025615</v>
+        <v>0.0025202</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="C48">
-        <v>0.0014422</v>
+        <v>0.0007438999999999999</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>32</v>
       </c>
       <c r="C49">
-        <v>0.0020269</v>
+        <v>0.0019956</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>32</v>
       </c>
       <c r="C50">
-        <v>0.0013142</v>
+        <v>0.0013024</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -1121,7 +1121,7 @@
         <v>32</v>
       </c>
       <c r="C51">
-        <v>0.002598899999999999</v>
+        <v>0.0025725</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -1135,7 +1135,7 @@
         <v>64</v>
       </c>
       <c r="C52">
-        <v>0.0168613</v>
+        <v>0.0171838</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>0.0093718</v>
+        <v>0.002988</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>64</v>
       </c>
       <c r="C54">
-        <v>0.0135943</v>
+        <v>0.0142777</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -1177,7 +1177,7 @@
         <v>64</v>
       </c>
       <c r="C55">
-        <v>0.004973300000000001</v>
+        <v>0.004972600000000001</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>0.0171851</v>
+        <v>0.0173022</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -1205,7 +1205,7 @@
         <v>128</v>
       </c>
       <c r="C57">
-        <v>0.1104541</v>
+        <v>0.1113246</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>0.07056939999999999</v>
+        <v>0.0138025</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>128</v>
       </c>
       <c r="C59">
-        <v>0.08971359999999999</v>
+        <v>0.09037300000000001</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -1247,7 +1247,7 @@
         <v>128</v>
       </c>
       <c r="C60">
-        <v>0.0216076</v>
+        <v>0.0217999</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -1261,7 +1261,7 @@
         <v>128</v>
       </c>
       <c r="C61">
-        <v>0.1110167</v>
+        <v>0.1117027</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -1275,7 +1275,7 @@
         <v>16</v>
       </c>
       <c r="C62">
-        <v>0.0006736</v>
+        <v>0.0005730000000000001</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -1289,7 +1289,7 @@
         <v>16</v>
       </c>
       <c r="C63">
-        <v>0.0003932000000000001</v>
+        <v>0.000196</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C64">
-        <v>0.000454</v>
+        <v>0.0004541000000000001</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -1317,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C65">
-        <v>0.0004305</v>
+        <v>0.0004201</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="C66">
-        <v>0.0007059999999999999</v>
+        <v>0.0005912000000000001</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -1345,7 +1345,7 @@
         <v>32</v>
       </c>
       <c r="C67">
-        <v>0.003875100000000001</v>
+        <v>0.0039611</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>0.0014195</v>
+        <v>0.0006352</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -1373,7 +1373,7 @@
         <v>32</v>
       </c>
       <c r="C69">
-        <v>0.002692</v>
+        <v>0.0026946</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
@@ -1387,7 +1387,7 @@
         <v>32</v>
       </c>
       <c r="C70">
-        <v>0.0013392</v>
+        <v>0.0013573</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -1401,7 +1401,7 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>0.0039451</v>
+        <v>0.0038404</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -1415,7 +1415,7 @@
         <v>64</v>
       </c>
       <c r="C72">
-        <v>0.0296328</v>
+        <v>0.0298233</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>0.0058033</v>
+        <v>0.0026319</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1443,7 +1443,7 @@
         <v>64</v>
       </c>
       <c r="C74">
-        <v>0.0183267</v>
+        <v>0.0186878</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -1457,7 +1457,7 @@
         <v>64</v>
       </c>
       <c r="C75">
-        <v>0.0050223</v>
+        <v>0.0050461</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -1471,7 +1471,7 @@
         <v>64</v>
       </c>
       <c r="C76">
-        <v>0.029346</v>
+        <v>0.0296411</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -1485,7 +1485,7 @@
         <v>128</v>
       </c>
       <c r="C77">
-        <v>0.2242598</v>
+        <v>0.2253527</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>0.0368362</v>
+        <v>0.0129174</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1513,7 +1513,7 @@
         <v>128</v>
       </c>
       <c r="C79">
-        <v>0.1254835</v>
+        <v>0.1292262</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -1527,7 +1527,7 @@
         <v>128</v>
       </c>
       <c r="C80">
-        <v>0.0206832</v>
+        <v>0.020667</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>128</v>
       </c>
       <c r="C81">
-        <v>0.2232106</v>
+        <v>0.2263918</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
@@ -1555,7 +1555,7 @@
         <v>16</v>
       </c>
       <c r="C82">
-        <v>0.0007793</v>
+        <v>0.0014131</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
@@ -1569,7 +1569,7 @@
         <v>16</v>
       </c>
       <c r="C83">
-        <v>0.0004352</v>
+        <v>0.0001992</v>
       </c>
       <c r="D83" t="s">
         <v>12</v>
@@ -1583,7 +1583,7 @@
         <v>16</v>
       </c>
       <c r="C84">
-        <v>0.0006098</v>
+        <v>0.0006092999999999999</v>
       </c>
       <c r="D84" t="s">
         <v>12</v>
@@ -1597,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="C85">
-        <v>0.0006093</v>
+        <v>0.0006078</v>
       </c>
       <c r="D85" t="s">
         <v>12</v>
@@ -1611,7 +1611,7 @@
         <v>16</v>
       </c>
       <c r="C86">
-        <v>0.0008636999999999999</v>
+        <v>0.0008003999999999999</v>
       </c>
       <c r="D86" t="s">
         <v>12</v>
@@ -1625,7 +1625,7 @@
         <v>32</v>
       </c>
       <c r="C87">
-        <v>0.0057743</v>
+        <v>0.005987899999999999</v>
       </c>
       <c r="D87" t="s">
         <v>12</v>
@@ -1639,7 +1639,7 @@
         <v>32</v>
       </c>
       <c r="C88">
-        <v>0.0015813</v>
+        <v>0.0005905999999999999</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -1653,7 +1653,7 @@
         <v>32</v>
       </c>
       <c r="C89">
-        <v>0.0035952</v>
+        <v>0.003592799999999999</v>
       </c>
       <c r="D89" t="s">
         <v>12</v>
@@ -1667,7 +1667,7 @@
         <v>32</v>
       </c>
       <c r="C90">
-        <v>0.0021138</v>
+        <v>0.0021167</v>
       </c>
       <c r="D90" t="s">
         <v>12</v>
@@ -1681,7 +1681,7 @@
         <v>32</v>
       </c>
       <c r="C91">
-        <v>0.0058417</v>
+        <v>0.0058376</v>
       </c>
       <c r="D91" t="s">
         <v>12</v>
@@ -1695,7 +1695,7 @@
         <v>64</v>
       </c>
       <c r="C92">
-        <v>0.0501117</v>
+        <v>0.0491155</v>
       </c>
       <c r="D92" t="s">
         <v>12</v>
@@ -1709,7 +1709,7 @@
         <v>64</v>
       </c>
       <c r="C93">
-        <v>0.0118541</v>
+        <v>0.0020338</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -1723,7 +1723,7 @@
         <v>64</v>
       </c>
       <c r="C94">
-        <v>0.023993</v>
+        <v>0.0239114</v>
       </c>
       <c r="D94" t="s">
         <v>12</v>
@@ -1737,7 +1737,7 @@
         <v>64</v>
       </c>
       <c r="C95">
-        <v>0.0080479</v>
+        <v>0.008017800000000002</v>
       </c>
       <c r="D95" t="s">
         <v>12</v>
@@ -1751,7 +1751,7 @@
         <v>64</v>
       </c>
       <c r="C96">
-        <v>0.0502154</v>
+        <v>0.0494466</v>
       </c>
       <c r="D96" t="s">
         <v>12</v>
@@ -1765,7 +1765,7 @@
         <v>128</v>
       </c>
       <c r="C97">
-        <v>0.340181</v>
+        <v>0.3437210000000001</v>
       </c>
       <c r="D97" t="s">
         <v>12</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>0.09822610000000001</v>
+        <v>0.0075347</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
@@ -1793,7 +1793,7 @@
         <v>128</v>
       </c>
       <c r="C99">
-        <v>0.1622748</v>
+        <v>0.1644629</v>
       </c>
       <c r="D99" t="s">
         <v>12</v>
@@ -1807,7 +1807,7 @@
         <v>128</v>
       </c>
       <c r="C100">
-        <v>0.03305300000000001</v>
+        <v>0.0331036</v>
       </c>
       <c r="D100" t="s">
         <v>12</v>
@@ -1821,7 +1821,7 @@
         <v>128</v>
       </c>
       <c r="C101">
-        <v>0.3422766</v>
+        <v>0.3435911</v>
       </c>
       <c r="D101" t="s">
         <v>12</v>
